--- a/mapEditor/editor.xlsx
+++ b/mapEditor/editor.xlsx
@@ -5,15 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KidyBean\Desktop\카이 자료\2026-01\프로그래밍의 이해\과제\CS20200-term-project-kidybean\term-proj\mapEditor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KidyBean\Desktop\Work\CS20200-term-project-kidybean\mapEditor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62441593-EA3F-44C4-885A-8B5433C32DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E042AC-3C64-4D54-AD36-068780CC9BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="21690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Stage 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Stage 5" sheetId="6" r:id="rId1"/>
+    <sheet name="Stage 4" sheetId="5" r:id="rId2"/>
+    <sheet name="Stage 3" sheetId="4" r:id="rId3"/>
+    <sheet name="Stage 2" sheetId="3" r:id="rId4"/>
+    <sheet name="Stage 1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2413" uniqueCount="7">
   <si>
     <t>#</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -55,6 +60,14 @@
   </si>
   <si>
     <t>S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -120,49 +133,11 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill patternType="darkHorizontal">
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightTrellis">
-          <fgColor theme="0"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightGrid">
-          <fgColor rgb="FF663300"/>
-          <bgColor theme="7" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray0625">
-          <fgColor theme="1"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="40">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
+          <bgColor theme="1" tint="0.34998626667073579"/>
         </patternFill>
       </fill>
     </dxf>
@@ -179,7 +154,293 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="1"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightGrid">
+          <fgColor rgb="FF663300"/>
+          <bgColor theme="7" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightTrellis">
+          <fgColor theme="0"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkHorizontal">
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="1" tint="0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="1"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightGrid">
+          <fgColor rgb="FF663300"/>
+          <bgColor theme="7" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightTrellis">
+          <fgColor theme="0"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkHorizontal">
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="1"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightGrid">
+          <fgColor rgb="FF663300"/>
+          <bgColor theme="7" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightTrellis">
+          <fgColor theme="0"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkHorizontal">
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="1"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightGrid">
+          <fgColor rgb="FF663300"/>
+          <bgColor theme="7" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightTrellis">
+          <fgColor theme="0"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkHorizontal">
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="1"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightGrid">
+          <fgColor rgb="FF663300"/>
+          <bgColor theme="7" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightTrellis">
+          <fgColor theme="0"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkHorizontal">
+          <bgColor theme="5" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -463,6 +724,4537 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06D65D9-B23F-4B84-9A3B-6FBE7D1E2D2E}">
+  <dimension ref="C4:AF39"/>
+  <sheetFormatPr defaultColWidth="5.83203125" defaultRowHeight="35" customHeight="1" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="16384" width="5.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="14:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="N4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="14:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="N5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="14:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="N6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="14:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="N7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="14:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="14:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="14:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="14:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="R11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="14:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="R12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="14:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="R13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="3:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AF24" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="V25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="R26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Q27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Q28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="T29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="17:28" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="R33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="17:28" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Q34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="17:28" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Q35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y35" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="17:28" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="U36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y36" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="17:28" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="U37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y37" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="17:28" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="U38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y38" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="17:28" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="U39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y39" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="K17:AF23 I17:I23 A1:XFD3 AG4:XFD4 I4:AF16 A41:XFD1048576 A40:Y40 BE5:XFD40 A4:A39 B4:H38">
+    <cfRule type="containsText" dxfId="39" priority="1" operator="containsText" text="D">
+      <formula>NOT(ISERROR(SEARCH("D",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="38" priority="2" operator="containsText" text="K">
+      <formula>NOT(ISERROR(SEARCH("K",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="37" priority="3" operator="containsText" text="B">
+      <formula>NOT(ISERROR(SEARCH("B",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="36" priority="4" operator="containsText" text="S">
+      <formula>NOT(ISERROR(SEARCH("S",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="35" priority="5" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="34" priority="6" operator="containsText" text="P">
+      <formula>NOT(ISERROR(SEARCH("P",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="33" priority="7" operator="containsText" text=".">
+      <formula>NOT(ISERROR(SEARCH(".",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="32" priority="8" operator="containsText" text="#">
+      <formula>NOT(ISERROR(SEARCH("#",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57EB36F3-812A-48A6-B8AC-F784915472CA}">
+  <dimension ref="A1:AP22"/>
+  <sheetFormatPr defaultColWidth="5.83203125" defaultRowHeight="35" customHeight="1" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="16384" width="5.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:42" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:42" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:42" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="N3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:42" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="R4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:42" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="N5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:42" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="H6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:42" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="H7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL7" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:42" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:42" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:42" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN10" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:42" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:42" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN12" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:42" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:42" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:42" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:42" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="L21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="L22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A1:XFD1048576">
+    <cfRule type="containsText" dxfId="31" priority="1" operator="containsText" text="D">
+      <formula>NOT(ISERROR(SEARCH("D",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="30" priority="2" operator="containsText" text="K">
+      <formula>NOT(ISERROR(SEARCH("K",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="29" priority="3" operator="containsText" text="B">
+      <formula>NOT(ISERROR(SEARCH("B",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="28" priority="4" operator="containsText" text="S">
+      <formula>NOT(ISERROR(SEARCH("S",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="27" priority="5" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="26" priority="6" operator="containsText" text="P">
+      <formula>NOT(ISERROR(SEARCH("P",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="25" priority="7" operator="containsText" text=".">
+      <formula>NOT(ISERROR(SEARCH(".",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="8" operator="containsText" text="#">
+      <formula>NOT(ISERROR(SEARCH("#",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15C89C8-EF31-4F9D-8EA5-25C2447B24BB}">
+  <dimension ref="B2:AN35"/>
+  <sheetFormatPr defaultColWidth="5.83203125" defaultRowHeight="35" customHeight="1" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="16384" width="5.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH12" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN16" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN17" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN18" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN19" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN20" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN21" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AD22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN22" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AD23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="3:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="3:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="3:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="3:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="3:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="3:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI29" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="3:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AH30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="3:40" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="17:27" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Q33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="17:27" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="T35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A1:XFD1048576">
+    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="D">
+      <formula>NOT(ISERROR(SEARCH("D",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="22" priority="2" operator="containsText" text="K">
+      <formula>NOT(ISERROR(SEARCH("K",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="B">
+      <formula>NOT(ISERROR(SEARCH("B",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="20" priority="4" operator="containsText" text="S">
+      <formula>NOT(ISERROR(SEARCH("S",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="19" priority="5" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="6" operator="containsText" text="P">
+      <formula>NOT(ISERROR(SEARCH("P",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="17" priority="7" operator="containsText" text=".">
+      <formula>NOT(ISERROR(SEARCH(".",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="8" operator="containsText" text="#">
+      <formula>NOT(ISERROR(SEARCH("#",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1342D1FF-65B6-4C9E-B07B-2E7297F19EE0}">
+  <dimension ref="B1:AC24"/>
+  <sheetFormatPr defaultColWidth="5.83203125" defaultRowHeight="35" customHeight="1" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="16384" width="5.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:24" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="L1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="2:24" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="L2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:24" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:24" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:24" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:24" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:24" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:24" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:24" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:24" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:24" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:24" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="11:29" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="11:29" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="11:29" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="11:29" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="11:29" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="11:29" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="11:29" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="11:29" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="S24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A1:XFD1048576">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="D">
+      <formula>NOT(ISERROR(SEARCH("D",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="K">
+      <formula>NOT(ISERROR(SEARCH("K",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="B">
+      <formula>NOT(ISERROR(SEARCH("B",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="S">
+      <formula>NOT(ISERROR(SEARCH("S",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="6" operator="containsText" text="P">
+      <formula>NOT(ISERROR(SEARCH("P",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text=".">
+      <formula>NOT(ISERROR(SEARCH(".",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="8" operator="containsText" text="#">
+      <formula>NOT(ISERROR(SEARCH("#",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH35"/>
   <sheetFormatPr defaultColWidth="5.83203125" defaultRowHeight="35" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -2322,7 +7114,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W20" s="1" t="s">
         <v>1</v>
@@ -3606,7 +8398,7 @@
         <v>1</v>
       </c>
       <c r="X35" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y35" s="1" t="s">
         <v>1</v>
@@ -3636,31 +8428,41 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="#">
-      <formula>NOT(ISERROR(SEARCH("#",A1)))</formula>
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="D">
+      <formula>NOT(ISERROR(SEARCH("D",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text=".">
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="K">
+      <formula>NOT(ISERROR(SEARCH("K",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="B">
+      <formula>NOT(ISERROR(SEARCH("B",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="S">
+      <formula>NOT(ISERROR(SEARCH("S",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="P">
+      <formula>NOT(ISERROR(SEARCH("P",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text=".">
       <formula>NOT(ISERROR(SEARCH(".",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="P">
-      <formula>NOT(ISERROR(SEARCH("P",A1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",A1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="S">
-      <formula>NOT(ISERROR(SEARCH("S",A1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="B">
-      <formula>NOT(ISERROR(SEARCH("B",A1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="K">
-      <formula>NOT(ISERROR(SEARCH("K",A1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="D">
-      <formula>NOT(ISERROR(SEARCH("D",A1)))</formula>
+    <cfRule type="containsText" dxfId="0" priority="8" operator="containsText" text="#">
+      <formula>NOT(ISERROR(SEARCH("#",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{472938D6-EC96-4473-8C0C-25934D7CB687}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/mapEditor/editor.xlsx
+++ b/mapEditor/editor.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KidyBean\Desktop\Work\CS20200-term-project-kidybean\mapEditor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E042AC-3C64-4D54-AD36-068780CC9BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A9F091-72D6-4604-ABA8-1D7635A3B9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Stage 5" sheetId="6" r:id="rId1"/>
-    <sheet name="Stage 4" sheetId="5" r:id="rId2"/>
-    <sheet name="Stage 3" sheetId="4" r:id="rId3"/>
-    <sheet name="Stage 2" sheetId="3" r:id="rId4"/>
-    <sheet name="Stage 1" sheetId="1" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId6"/>
+    <sheet name="Stage 6" sheetId="7" r:id="rId1"/>
+    <sheet name="Stage 5" sheetId="6" r:id="rId2"/>
+    <sheet name="Stage 4" sheetId="5" r:id="rId3"/>
+    <sheet name="Stage 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Stage 2" sheetId="3" r:id="rId5"/>
+    <sheet name="Stage 1" sheetId="1" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2413" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2796" uniqueCount="20">
   <si>
     <t>#</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,6 +69,58 @@
   </si>
   <si>
     <t>K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -133,7 +186,69 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="48">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="1"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightGrid">
+          <fgColor rgb="FF663300"/>
+          <bgColor theme="7" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightTrellis">
+          <fgColor theme="0"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkHorizontal">
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -724,6 +839,1254 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51977DFA-8748-4024-8482-7215D7E83F47}">
+  <dimension ref="E15:AK43"/>
+  <sheetFormatPr defaultColWidth="5.83203125" defaultRowHeight="35" customHeight="1" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="16384" width="5.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="15" spans="13:18" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="13:18" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="5:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="5:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="5:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="5:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="5:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="5:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="5:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="5:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK24" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="5:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK25" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="5:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AC26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="5:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="N27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="5:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="5:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="5:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG30" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="5:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="L31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X31" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="5:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="7:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH33" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="7:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH34" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="7:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH35" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="7:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH36" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="7:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="L37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="7:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="N38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG38" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="7:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="N39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="7:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="N40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ40" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="7:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="N41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="7:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="N42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="7:37" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="N43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A1:XFD1048576">
+    <cfRule type="containsText" dxfId="47" priority="1" operator="containsText" text="D">
+      <formula>NOT(ISERROR(SEARCH("D",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="46" priority="2" operator="containsText" text="K">
+      <formula>NOT(ISERROR(SEARCH("K",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="45" priority="3" operator="containsText" text="B">
+      <formula>NOT(ISERROR(SEARCH("B",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="44" priority="4" operator="containsText" text="S">
+      <formula>NOT(ISERROR(SEARCH("S",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="43" priority="5" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="42" priority="6" operator="containsText" text="P">
+      <formula>NOT(ISERROR(SEARCH("P",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="41" priority="7" operator="containsText" text=".">
+      <formula>NOT(ISERROR(SEARCH(".",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="40" priority="8" operator="containsText" text="#">
+      <formula>NOT(ISERROR(SEARCH("#",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06D65D9-B23F-4B84-9A3B-6FBE7D1E2D2E}">
   <dimension ref="C4:AF39"/>
   <sheetFormatPr defaultColWidth="5.83203125" defaultRowHeight="35" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -1561,7 +2924,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="K17:AF23 I17:I23 A1:XFD3 AG4:XFD4 I4:AF16 A41:XFD1048576 A40:Y40 BE5:XFD40 A4:A39 B4:H38">
+  <conditionalFormatting sqref="A1:XFD3 AG4:XFD4 I4:AF16 B4:H38 A4:A39 BE5:XFD40 I17:I23 K17:AF23 A40:Y40 A41:XFD1048576">
     <cfRule type="containsText" dxfId="39" priority="1" operator="containsText" text="D">
       <formula>NOT(ISERROR(SEARCH("D",A1)))</formula>
     </cfRule>
@@ -1592,7 +2955,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57EB36F3-812A-48A6-B8AC-F784915472CA}">
   <dimension ref="A1:AP22"/>
   <sheetFormatPr defaultColWidth="5.83203125" defaultRowHeight="35" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -2571,7 +3934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15C89C8-EF31-4F9D-8EA5-25C2447B24BB}">
   <dimension ref="B2:AN35"/>
   <sheetFormatPr defaultColWidth="5.83203125" defaultRowHeight="35" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -3984,7 +5347,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1342D1FF-65B6-4C9E-B07B-2E7297F19EE0}">
   <dimension ref="B1:AC24"/>
   <sheetFormatPr defaultColWidth="5.83203125" defaultRowHeight="35" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -5254,7 +6617,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH35"/>
   <sheetFormatPr defaultColWidth="5.83203125" defaultRowHeight="35" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -8457,7 +9820,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{472938D6-EC96-4473-8C0C-25934D7CB687}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
